--- a/data/externalStats/File1/RPT_RPT7294033893830TY_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT7294033893830TY_externalStats.xlsx
@@ -2258,7 +2258,7 @@
         <v>11053681.77593989</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>14824.51869790835</v>
+        <v>14824.51869790836</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>6188704.374589608</v>
+        <v>6188704.374589607</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>3352.283312</v>
@@ -2623,7 +2623,7 @@
         <v>5634318.814640129</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>752.3329949999999</v>
+        <v>752.332995</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>5231411.651656954</v>
+        <v>5231411.651656953</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>780.9839425823877</v>
+        <v>780.9839425823878</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -2854,7 +2854,7 @@
         <v>2901313.69343935</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>354.0840958925122</v>
+        <v>354.0840958925123</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -4285,7 +4285,7 @@
         <v>2550857.543178587</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>6706.464778411768</v>
+        <v>6706.464778411767</v>
       </c>
     </row>
     <row r="58">
@@ -4310,13 +4310,13 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410512</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -4325,22 +4325,22 @@
         <v>5043.97753572962</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237324</v>
+        <v>3672.153688237323</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831595</v>
+        <v>276.6926051831597</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842925</v>
+        <v>5127.579913842924</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -4352,7 +4352,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -4397,13 +4397,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>4111.798092690688</v>
+        <v>4111.798092690687</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>4472.362957366963</v>
+        <v>4472.362957366962</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -4412,13 +4412,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532679</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597412</v>
+        <v>4497.071348597411</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.64908945068</v>
+        <v>4902.649089450679</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -4556,13 +4556,13 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.035876790112</v>
+        <v>710.0358767901123</v>
       </c>
       <c r="L61" s="131" t="n">
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894159</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
@@ -4571,13 +4571,13 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141091</v>
+        <v>760.0653829141094</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>237.7472517739969</v>
+        <v>237.747251773997</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193555</v>
       </c>
       <c r="T61" s="132" t="n">
         <v>4406.934138657396</v>
@@ -4586,16 +4586,16 @@
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.2490276888539</v>
+        <v>816.249027688854</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252182</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -4609,7 +4609,7 @@
         <v>1378098.727412944</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>4568.302287999999</v>
+        <v>4568.302288</v>
       </c>
     </row>
     <row r="62">
@@ -4715,37 +4715,37 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862924</v>
+        <v>2315.017224862917</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407942</v>
+        <v>410.0571917407933</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810831</v>
+        <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375976</v>
+        <v>7725.854158375966</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303859</v>
+        <v>2462.596460303845</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224312</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266722</v>
+        <v>151.8055148266712</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469682</v>
+        <v>8533.61799146967</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.658250704619</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>448.2773868014756</v>
@@ -4754,10 +4754,10 @@
         <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865834</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292743</v>
+        <v>9544.249776292738</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -5066,16 +5066,16 @@
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233701</v>
+        <v>1367.292909233702</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>3448.841300635403</v>
+        <v>3448.841300635402</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288214</v>
+        <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700118</v>
@@ -5084,10 +5084,10 @@
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460277</v>
+        <v>3796.051969460278</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>989013.9075189302</v>
+        <v>989013.90751893</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>2740.1603206045</v>
@@ -5126,10 +5126,10 @@
         <v>45224</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.58614152437</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>6296.901716791416</v>
+        <v>6296.901716791415</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>2411.363160259785</v>
@@ -5138,16 +5138,16 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342015</v>
+        <v>62122.69724342014</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.29188665193</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411188</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870797</v>
+        <v>2439.116021870798</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>14003.78216636889</v>
@@ -5156,7 +5156,7 @@
         <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.71923906604</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>6878.522835275839</v>
@@ -5168,7 +5168,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.35109118339</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5686,10 +5686,10 @@
         <v>183.3291939762257</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399726</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -5698,13 +5698,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -5750,7 +5750,7 @@
         <v>311.9992424177221</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>358.769161908742</v>
+        <v>358.7691619087421</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -5872,25 +5872,25 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486968</v>
+        <v>2697.069435486967</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.21015374407511</v>
+        <v>51.2101537440751</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2871.031146169767</v>
+        <v>2871.031146169766</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277547</v>
+        <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>62.88229397936019</v>
@@ -5899,7 +5899,7 @@
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.051936416378</v>
+        <v>3183.051936416379</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3245.047703850661</v>
@@ -6354,7 +6354,7 @@
         <v>57365.21870971905</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>2922.954135118952</v>
+        <v>2922.954135118953</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>1418321.957026413</v>
@@ -6876,7 +6876,7 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748544</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
@@ -6891,13 +6891,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901524</v>
+        <v>3803.886503901523</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483361</v>
+        <v>289.1404209483363</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -6906,13 +6906,13 @@
         <v>5315.894937306298</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107065</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -6964,13 +6964,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665504</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4874.628103683081</v>
+        <v>4874.62810368308</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049631</v>
+        <v>5331.24670904963</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -7080,13 +7080,13 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771899</v>
+        <v>821.8541182771902</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410618</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>7069.112073998888</v>
@@ -7095,19 +7095,19 @@
         <v>5816.280603427482</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.396351492128</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.629545753357</v>
+        <v>300.6295457533572</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008075</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>7589.986075073774</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.65599672089</v>
+        <v>6250.655996720889</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
@@ -7116,10 +7116,10 @@
         <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299143</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255578</v>
+        <v>8153.039091255577</v>
       </c>
     </row>
     <row r="98">
@@ -7220,10 +7220,10 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571751</v>
+        <v>6263.925439571749</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136657</v>
+        <v>9129.730529136656</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2462.596460303757</v>
@@ -7250,7 +7250,7 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578741</v>
+        <v>7864.526914578742</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>11117.97029900591</v>
@@ -7522,7 +7522,7 @@
         <v>59655.70951589625</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>5336.818379074632</v>
+        <v>5336.818379074633</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1482669.911579746</v>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>36479108.3909279</v>
+        <v>36479108.39092791</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>47681.20374516815</v>
@@ -9076,7 +9076,7 @@
         <v>8104574.014232036</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>4224.614475448639</v>
+        <v>4224.61447544864</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>7261041.493413352</v>
+        <v>7261041.493413353</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>911.6395066912501</v>
@@ -9893,7 +9893,7 @@
         <v>1751703.99415768</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>2220.603683210644</v>
+        <v>2220.603683210645</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -9970,7 +9970,7 @@
         <v>1677255.769387772</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>3262.522261530559</v>
+        <v>3262.52226153056</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -10644,7 +10644,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>3737245.531379696</v>
+        <v>3737245.531379695</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>10006.56508121006</v>
@@ -10725,10 +10725,10 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2927155.577501255</v>
+        <v>2927155.577501254</v>
       </c>
       <c r="AH56" s="56" t="n">
-        <v>250.2622030851889</v>
+        <v>250.2622030851888</v>
       </c>
     </row>
     <row r="57">
@@ -10834,13 +10834,13 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410512</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -10849,22 +10849,22 @@
         <v>5043.97753572962</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237324</v>
+        <v>3672.153688237323</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831595</v>
+        <v>276.6926051831597</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842925</v>
+        <v>5127.579913842924</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -10887,10 +10887,10 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1945845.153215983</v>
+        <v>1945845.153215984</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>6395.6232032</v>
+        <v>6395.623203199999</v>
       </c>
     </row>
     <row r="59">
@@ -10921,13 +10921,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>4111.798092690688</v>
+        <v>4111.798092690687</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>4472.362957366963</v>
+        <v>4472.362957366962</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -10936,13 +10936,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532679</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597412</v>
+        <v>4497.071348597411</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.64908945068</v>
+        <v>4902.649089450679</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -11080,13 +11080,13 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.035876790112</v>
+        <v>710.0358767901123</v>
       </c>
       <c r="L61" s="131" t="n">
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894159</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
@@ -11095,13 +11095,13 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141091</v>
+        <v>760.0653829141094</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>237.7472517739969</v>
+        <v>237.747251773997</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193555</v>
       </c>
       <c r="T61" s="132" t="n">
         <v>4406.934138657396</v>
@@ -11110,16 +11110,16 @@
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.2490276888539</v>
+        <v>816.249027688854</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252182</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -11239,37 +11239,37 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862924</v>
+        <v>2315.017224862917</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407942</v>
+        <v>410.0571917407933</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810831</v>
+        <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375976</v>
+        <v>7725.854158375966</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303859</v>
+        <v>2462.596460303845</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224312</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266722</v>
+        <v>151.8055148266712</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469682</v>
+        <v>8533.61799146967</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.658250704619</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>448.2773868014756</v>
@@ -11278,10 +11278,10 @@
         <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865834</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292743</v>
+        <v>9544.249776292738</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -11590,16 +11590,16 @@
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233701</v>
+        <v>1367.292909233702</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>3448.841300635403</v>
+        <v>3448.841300635402</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288214</v>
+        <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700118</v>
@@ -11608,10 +11608,10 @@
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460277</v>
+        <v>3796.051969460278</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -11622,7 +11622,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>840876.1331557619</v>
+        <v>840876.133155762</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>2581.255131689318</v>
@@ -11650,10 +11650,10 @@
         <v>45224</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.58614152437</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>6296.901716791416</v>
+        <v>6296.901716791415</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>2411.363160259785</v>
@@ -11662,16 +11662,16 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342015</v>
+        <v>62122.69724342014</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.29188665193</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411188</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870797</v>
+        <v>2439.116021870798</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>14003.78216636889</v>
@@ -11680,7 +11680,7 @@
         <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.71923906604</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>6878.522835275839</v>
@@ -11692,7 +11692,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.35109118339</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -12210,10 +12210,10 @@
         <v>183.3291939762257</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399726</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -12222,13 +12222,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -12274,7 +12274,7 @@
         <v>311.9992424177221</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>358.769161908742</v>
+        <v>358.7691619087421</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -12396,25 +12396,25 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486968</v>
+        <v>2697.069435486967</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.21015374407511</v>
+        <v>51.2101537440751</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2871.031146169767</v>
+        <v>2871.031146169766</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277547</v>
+        <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>62.88229397936019</v>
@@ -12423,7 +12423,7 @@
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.051936416378</v>
+        <v>3183.051936416379</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3245.047703850661</v>
@@ -12878,7 +12878,7 @@
         <v>57365.21870971905</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>2922.954135118952</v>
+        <v>2922.954135118953</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>1418321.957026413</v>
@@ -13400,7 +13400,7 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748544</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
@@ -13415,13 +13415,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901524</v>
+        <v>3803.886503901523</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483361</v>
+        <v>289.1404209483363</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -13430,13 +13430,13 @@
         <v>5315.894937306298</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107065</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -13488,13 +13488,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665504</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4874.628103683081</v>
+        <v>4874.62810368308</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049631</v>
+        <v>5331.24670904963</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -13604,13 +13604,13 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771899</v>
+        <v>821.8541182771902</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410618</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>7069.112073998888</v>
@@ -13619,19 +13619,19 @@
         <v>5816.280603427482</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.396351492128</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.629545753357</v>
+        <v>300.6295457533572</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008075</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>7589.986075073774</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.65599672089</v>
+        <v>6250.655996720889</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
@@ -13640,10 +13640,10 @@
         <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299143</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255578</v>
+        <v>8153.039091255577</v>
       </c>
     </row>
     <row r="98">
@@ -13744,10 +13744,10 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571751</v>
+        <v>6263.925439571749</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136657</v>
+        <v>9129.730529136656</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2462.596460303757</v>
@@ -13774,7 +13774,7 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578741</v>
+        <v>7864.526914578742</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>11117.97029900591</v>
@@ -14046,7 +14046,7 @@
         <v>59655.70951589625</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>5336.818379074632</v>
+        <v>5336.818379074633</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1482669.911579746</v>
@@ -15149,10 +15149,10 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>45226804.31269631</v>
+        <v>45226804.31269629</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>57217.44053621583</v>
+        <v>57217.44053621582</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -15600,7 +15600,7 @@
         <v>10338954.44928697</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>5158.465505246562</v>
+        <v>5158.465505246561</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -15979,7 +15979,7 @@
         <v>3399938.26107962</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>370.475820109104</v>
+        <v>370.4758201091039</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -16196,7 +16196,7 @@
         <v>2565277.66149139</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>8051.17770688</v>
+        <v>8051.177706879999</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -17358,13 +17358,13 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410512</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -17373,22 +17373,22 @@
         <v>5043.97753572962</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237324</v>
+        <v>3672.153688237323</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831595</v>
+        <v>276.6926051831597</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842925</v>
+        <v>5127.579913842924</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -17400,7 +17400,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -17414,7 +17414,7 @@
         <v>2792867.850268204</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>8953.872484479998</v>
+        <v>8953.87248448</v>
       </c>
     </row>
     <row r="59">
@@ -17445,13 +17445,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>4111.798092690688</v>
+        <v>4111.798092690687</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>4472.362957366963</v>
+        <v>4472.362957366962</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -17460,13 +17460,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532679</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597412</v>
+        <v>4497.071348597411</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.64908945068</v>
+        <v>4902.649089450679</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -17604,13 +17604,13 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.035876790112</v>
+        <v>710.0358767901123</v>
       </c>
       <c r="L61" s="131" t="n">
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894159</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
@@ -17619,13 +17619,13 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141091</v>
+        <v>760.0653829141094</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>237.7472517739969</v>
+        <v>237.747251773997</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193555</v>
       </c>
       <c r="T61" s="132" t="n">
         <v>4406.934138657396</v>
@@ -17634,16 +17634,16 @@
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.2490276888539</v>
+        <v>816.249027688854</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252182</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -17763,37 +17763,37 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862924</v>
+        <v>2315.017224862917</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407942</v>
+        <v>410.0571917407933</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810831</v>
+        <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375976</v>
+        <v>7725.854158375966</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303859</v>
+        <v>2462.596460303845</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224312</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266722</v>
+        <v>151.8055148266712</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469682</v>
+        <v>8533.61799146967</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.658250704619</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>448.2773868014756</v>
@@ -17802,10 +17802,10 @@
         <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865834</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292743</v>
+        <v>9544.249776292738</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="AG64" s="122" t="n">
-        <v>1076065.182731765</v>
+        <v>1076065.182731766</v>
       </c>
       <c r="AH64" s="56" t="n">
         <v>4715.065128560274</v>
@@ -18065,7 +18065,7 @@
         </is>
       </c>
       <c r="AG66" s="122" t="n">
-        <v>830147.9715411521</v>
+        <v>830147.971541152</v>
       </c>
       <c r="AH66" s="56" t="n">
         <v>524.462996491248</v>
@@ -18114,16 +18114,16 @@
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233701</v>
+        <v>1367.292909233702</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>3448.841300635403</v>
+        <v>3448.841300635402</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288214</v>
+        <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700118</v>
@@ -18132,10 +18132,10 @@
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460277</v>
+        <v>3796.051969460278</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -18174,10 +18174,10 @@
         <v>45224</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.58614152437</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>6296.901716791416</v>
+        <v>6296.901716791415</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>2411.363160259785</v>
@@ -18186,16 +18186,16 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342015</v>
+        <v>62122.69724342014</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.29188665193</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411188</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870797</v>
+        <v>2439.116021870798</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>14003.78216636889</v>
@@ -18204,7 +18204,7 @@
         <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.71923906604</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>6878.522835275839</v>
@@ -18216,7 +18216,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.35109118339</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18734,10 +18734,10 @@
         <v>183.3291939762257</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399726</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -18746,13 +18746,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -18798,7 +18798,7 @@
         <v>311.9992424177221</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>358.769161908742</v>
+        <v>358.7691619087421</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -18920,25 +18920,25 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486968</v>
+        <v>2697.069435486967</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.21015374407511</v>
+        <v>51.2101537440751</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2871.031146169767</v>
+        <v>2871.031146169766</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277547</v>
+        <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>62.88229397936019</v>
@@ -18947,7 +18947,7 @@
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.051936416378</v>
+        <v>3183.051936416379</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3245.047703850661</v>
@@ -19402,7 +19402,7 @@
         <v>57365.21870971905</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>2922.954135118952</v>
+        <v>2922.954135118953</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>1418321.957026413</v>
@@ -19924,7 +19924,7 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748544</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
@@ -19939,13 +19939,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901524</v>
+        <v>3803.886503901523</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483361</v>
+        <v>289.1404209483363</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -19954,13 +19954,13 @@
         <v>5315.894937306298</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107065</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -20012,13 +20012,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665504</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4874.628103683081</v>
+        <v>4874.62810368308</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049631</v>
+        <v>5331.24670904963</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -20128,13 +20128,13 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771899</v>
+        <v>821.8541182771902</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410618</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>7069.112073998888</v>
@@ -20143,19 +20143,19 @@
         <v>5816.280603427482</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.396351492128</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.629545753357</v>
+        <v>300.6295457533572</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008075</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>7589.986075073774</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.65599672089</v>
+        <v>6250.655996720889</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
@@ -20164,10 +20164,10 @@
         <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299143</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255578</v>
+        <v>8153.039091255577</v>
       </c>
     </row>
     <row r="98">
@@ -20268,10 +20268,10 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571751</v>
+        <v>6263.925439571749</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136657</v>
+        <v>9129.730529136656</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2462.596460303757</v>
@@ -20298,7 +20298,7 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578741</v>
+        <v>7864.526914578742</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>11117.97029900591</v>
@@ -20570,7 +20570,7 @@
         <v>59655.70951589625</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>5336.818379074632</v>
+        <v>5336.818379074633</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1482669.911579746</v>
@@ -21676,7 +21676,7 @@
         <v>55708663.09676258</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379247</v>
+        <v>68660.92484379245</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -21769,7 +21769,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>1589.450980859626</v>
+        <v>1589.450980859627</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -21984,7 +21984,7 @@
         <v>13031677.99235527</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>6257.992427689867</v>
+        <v>6257.992427689866</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -22121,7 +22121,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>11120783.40219731</v>
+        <v>11120783.4021973</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>13115.78537471264</v>
@@ -22269,7 +22269,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6528556.355378518</v>
+        <v>6528556.355378517</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>833.5527624453042</v>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>2006758.971569034</v>
+        <v>2006758.971569033</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>3570.123843302602</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>9810448.624385368</v>
+        <v>9810448.624385366</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>23659.13977320257</v>
@@ -23882,13 +23882,13 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410512</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -23897,22 +23897,22 @@
         <v>5043.97753572962</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237324</v>
+        <v>3672.153688237323</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831595</v>
+        <v>276.6926051831597</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842925</v>
+        <v>5127.579913842924</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -23969,13 +23969,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>4111.798092690688</v>
+        <v>4111.798092690687</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>4472.362957366963</v>
+        <v>4472.362957366962</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -23984,13 +23984,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532679</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597412</v>
+        <v>4497.071348597411</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.64908945068</v>
+        <v>4902.649089450679</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -24128,13 +24128,13 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.035876790112</v>
+        <v>710.0358767901123</v>
       </c>
       <c r="L61" s="131" t="n">
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894159</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
@@ -24143,13 +24143,13 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141091</v>
+        <v>760.0653829141094</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>237.7472517739969</v>
+        <v>237.747251773997</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193555</v>
       </c>
       <c r="T61" s="132" t="n">
         <v>4406.934138657396</v>
@@ -24158,16 +24158,16 @@
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.2490276888539</v>
+        <v>816.249027688854</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252182</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -24287,37 +24287,37 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862924</v>
+        <v>2315.017224862917</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407942</v>
+        <v>410.0571917407933</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810831</v>
+        <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375976</v>
+        <v>7725.854158375966</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303859</v>
+        <v>2462.596460303845</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224312</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266722</v>
+        <v>151.8055148266712</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469682</v>
+        <v>8533.61799146967</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.658250704619</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>448.2773868014756</v>
@@ -24326,10 +24326,10 @@
         <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865834</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292743</v>
+        <v>9544.249776292738</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -24638,16 +24638,16 @@
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233701</v>
+        <v>1367.292909233702</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>3448.841300635403</v>
+        <v>3448.841300635402</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288214</v>
+        <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700118</v>
@@ -24656,10 +24656,10 @@
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460277</v>
+        <v>3796.051969460278</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -24698,10 +24698,10 @@
         <v>45224</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.58614152437</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>6296.901716791416</v>
+        <v>6296.901716791415</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>2411.363160259785</v>
@@ -24710,16 +24710,16 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342015</v>
+        <v>62122.69724342014</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.29188665193</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411188</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870797</v>
+        <v>2439.116021870798</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>14003.78216636889</v>
@@ -24728,7 +24728,7 @@
         <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.71923906604</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>6878.522835275839</v>
@@ -24740,7 +24740,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.35109118339</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -25258,10 +25258,10 @@
         <v>183.3291939762257</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399726</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -25270,13 +25270,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -25322,7 +25322,7 @@
         <v>311.9992424177221</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>358.769161908742</v>
+        <v>358.7691619087421</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -25444,25 +25444,25 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486968</v>
+        <v>2697.069435486967</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.21015374407511</v>
+        <v>51.2101537440751</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2871.031146169767</v>
+        <v>2871.031146169766</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277547</v>
+        <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>62.88229397936019</v>
@@ -25471,7 +25471,7 @@
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.051936416378</v>
+        <v>3183.051936416379</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3245.047703850661</v>
@@ -25926,7 +25926,7 @@
         <v>57365.21870971905</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>2922.954135118952</v>
+        <v>2922.954135118953</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>1418321.957026413</v>
@@ -26448,7 +26448,7 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748544</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
@@ -26463,13 +26463,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901524</v>
+        <v>3803.886503901523</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483361</v>
+        <v>289.1404209483363</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -26478,13 +26478,13 @@
         <v>5315.894937306298</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107065</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -26536,13 +26536,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665504</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4874.628103683081</v>
+        <v>4874.62810368308</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049631</v>
+        <v>5331.24670904963</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -26652,13 +26652,13 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771899</v>
+        <v>821.8541182771902</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410618</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>7069.112073998888</v>
@@ -26667,19 +26667,19 @@
         <v>5816.280603427482</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.396351492128</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.629545753357</v>
+        <v>300.6295457533572</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008075</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>7589.986075073774</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.65599672089</v>
+        <v>6250.655996720889</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
@@ -26688,10 +26688,10 @@
         <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299143</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255578</v>
+        <v>8153.039091255577</v>
       </c>
     </row>
     <row r="98">
@@ -26792,10 +26792,10 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571751</v>
+        <v>6263.925439571749</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136657</v>
+        <v>9129.730529136656</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2462.596460303757</v>
@@ -26822,7 +26822,7 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578741</v>
+        <v>7864.526914578742</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>11117.97029900591</v>
@@ -27094,7 +27094,7 @@
         <v>59655.70951589625</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>5336.818379074632</v>
+        <v>5336.818379074633</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1482669.911579746</v>
@@ -28200,7 +28200,7 @@
         <v>69272530.81205235</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.1061648711</v>
+        <v>82393.10616487113</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28277,7 +28277,7 @@
         <v>30879003.96205981</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>2045.210599589362</v>
+        <v>2045.210599589361</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -28508,7 +28508,7 @@
         <v>16598675.10338615</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>7591.883513651962</v>
+        <v>7591.883513651963</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>14570481.40100322</v>
+        <v>14570481.40100323</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>1523.105781032218</v>
@@ -28793,10 +28793,10 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>7082919.956535398</v>
+        <v>7082919.956535397</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>850.356497390649</v>
+        <v>850.3564973906491</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -29104,7 +29104,7 @@
         <v>3959648.639615083</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>385.5828701423581</v>
+        <v>385.5828701423582</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -29404,7 +29404,7 @@
         </is>
       </c>
       <c r="AN41" s="58" t="n">
-        <v>418.9450962243398</v>
+        <v>418.9450962243397</v>
       </c>
     </row>
     <row r="42">
@@ -29616,7 +29616,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>2260678.222648064</v>
+        <v>2260678.222648065</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>2957.226786839574</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>93034677.71118248</v>
+        <v>93034677.71118249</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>9156.756912025599</v>
@@ -30219,7 +30219,7 @@
         <v>5734707.282319224</v>
       </c>
       <c r="AH55" s="56" t="n">
-        <v>17549.59006958079</v>
+        <v>17549.5900695808</v>
       </c>
     </row>
     <row r="56">
@@ -30406,13 +30406,13 @@
         <v>4914</v>
       </c>
       <c r="J58" s="130" t="n">
-        <v>3621.760652410513</v>
+        <v>3621.760652410512</v>
       </c>
       <c r="K58" s="131" t="n">
         <v>1147.012970144039</v>
       </c>
       <c r="L58" s="131" t="n">
-        <v>275.2039131750689</v>
+        <v>275.2039131750688</v>
       </c>
       <c r="M58" s="131" t="n">
         <v>0</v>
@@ -30421,22 +30421,22 @@
         <v>5043.97753572962</v>
       </c>
       <c r="P58" s="130" t="n">
-        <v>3672.153688237324</v>
+        <v>3672.153688237323</v>
       </c>
       <c r="Q58" s="131" t="n">
         <v>1178.733620422441</v>
       </c>
       <c r="R58" s="131" t="n">
-        <v>276.6926051831595</v>
+        <v>276.6926051831597</v>
       </c>
       <c r="S58" s="131" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>5127.579913842925</v>
+        <v>5127.579913842924</v>
       </c>
       <c r="V58" s="130" t="n">
-        <v>3728.347202327302</v>
+        <v>3728.347202327301</v>
       </c>
       <c r="W58" s="131" t="n">
         <v>1211.320813085391</v>
@@ -30448,7 +30448,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="132" t="n">
-        <v>5217.744981077949</v>
+        <v>5217.744981077948</v>
       </c>
       <c r="AE58" s="121" t="n">
         <v>10</v>
@@ -30493,13 +30493,13 @@
         <v>0</v>
       </c>
       <c r="L59" s="131" t="n">
-        <v>360.5648646762757</v>
+        <v>360.5648646762758</v>
       </c>
       <c r="M59" s="131" t="n">
-        <v>4111.798092690688</v>
+        <v>4111.798092690687</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>4472.362957366963</v>
+        <v>4472.362957366962</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -30508,13 +30508,13 @@
         <v>0</v>
       </c>
       <c r="R59" s="131" t="n">
-        <v>405.5777408532679</v>
+        <v>405.5777408532681</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>4497.071348597412</v>
+        <v>4497.071348597411</v>
       </c>
       <c r="T59" s="132" t="n">
-        <v>4902.64908945068</v>
+        <v>4902.649089450679</v>
       </c>
       <c r="V59" s="130" t="n">
         <v>0</v>
@@ -30540,7 +30540,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>2703814.779673402</v>
+        <v>2703814.779673403</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>0</v>
@@ -30652,13 +30652,13 @@
         <v>2710.474833260433</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>710.035876790112</v>
+        <v>710.0358767901123</v>
       </c>
       <c r="L61" s="131" t="n">
         <v>227.8577587891603</v>
       </c>
       <c r="M61" s="131" t="n">
-        <v>549.7124589894162</v>
+        <v>549.7124589894159</v>
       </c>
       <c r="N61" s="132" t="n">
         <v>4198.080927829122</v>
@@ -30667,13 +30667,13 @@
         <v>2848.462218149934</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>760.0653829141091</v>
+        <v>760.0653829141094</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>237.7472517739969</v>
+        <v>237.747251773997</v>
       </c>
       <c r="S61" s="131" t="n">
-        <v>560.6592858193557</v>
+        <v>560.6592858193555</v>
       </c>
       <c r="T61" s="132" t="n">
         <v>4406.934138657396</v>
@@ -30682,16 +30682,16 @@
         <v>3005.608292870229</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>816.2490276888539</v>
+        <v>816.249027688854</v>
       </c>
       <c r="X61" s="131" t="n">
         <v>248.7069152504284</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>582.308785025218</v>
+        <v>582.3087850252182</v>
       </c>
       <c r="Z61" s="132" t="n">
-        <v>4652.87302083473</v>
+        <v>4652.873020834729</v>
       </c>
       <c r="AE61" s="121" t="n">
         <v>13</v>
@@ -30811,37 +30811,37 @@
         <v>3167</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2315.017224862924</v>
+        <v>2315.017224862917</v>
       </c>
       <c r="K63" s="131" t="n">
-        <v>410.0571917407942</v>
+        <v>410.0571917407933</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>140.730672961427</v>
+        <v>140.7306729614265</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>4860.049068810831</v>
+        <v>4860.049068810829</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>7725.854158375976</v>
+        <v>7725.854158375966</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2462.596460303859</v>
+        <v>2462.596460303845</v>
       </c>
       <c r="Q63" s="131" t="n">
         <v>422.0057850224312</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>151.8055148266722</v>
+        <v>151.8055148266712</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>5497.21023131672</v>
+        <v>5497.210231316722</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>8533.617991469682</v>
+        <v>8533.61799146967</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2639.658250704626</v>
+        <v>2639.658250704619</v>
       </c>
       <c r="W63" s="131" t="n">
         <v>448.2773868014756</v>
@@ -30850,10 +30850,10 @@
         <v>165.5077469208086</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>6290.806391865834</v>
+        <v>6290.806391865835</v>
       </c>
       <c r="Z63" s="132" t="n">
-        <v>9544.249776292743</v>
+        <v>9544.249776292738</v>
       </c>
       <c r="AE63" s="121" t="n">
         <v>15</v>
@@ -30867,7 +30867,7 @@
         <v>1178091.60903617</v>
       </c>
       <c r="AH63" s="56" t="n">
-        <v>4951.63903452981</v>
+        <v>4951.639034529809</v>
       </c>
     </row>
     <row r="64">
@@ -31162,16 +31162,16 @@
         <v>4092.276733052207</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>1367.292909233701</v>
+        <v>1367.292909233702</v>
       </c>
       <c r="S67" s="140" t="n">
-        <v>3448.841300635403</v>
+        <v>3448.841300635402</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>41401.49046288214</v>
+        <v>41401.49046288215</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>34025.1054931639</v>
+        <v>34025.10549316389</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>4402.675607700118</v>
@@ -31180,10 +31180,10 @@
         <v>1383.301697099319</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>3796.051969460277</v>
+        <v>3796.051969460278</v>
       </c>
       <c r="Z67" s="141" t="n">
-        <v>43607.13476742362</v>
+        <v>43607.13476742361</v>
       </c>
       <c r="AE67" s="121" t="n">
         <v>19</v>
@@ -31222,10 +31222,10 @@
         <v>45224</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>40517.58614152438</v>
+        <v>40517.58614152437</v>
       </c>
       <c r="K68" s="143" t="n">
-        <v>6296.901716791416</v>
+        <v>6296.901716791415</v>
       </c>
       <c r="L68" s="143" t="n">
         <v>2411.363160259785</v>
@@ -31234,16 +31234,16 @@
         <v>12896.84622484457</v>
       </c>
       <c r="N68" s="144" t="n">
-        <v>62122.69724342015</v>
+        <v>62122.69724342014</v>
       </c>
       <c r="P68" s="142" t="n">
-        <v>41476.29188665195</v>
+        <v>41476.29188665193</v>
       </c>
       <c r="Q68" s="143" t="n">
         <v>6453.081521411188</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2439.116021870797</v>
+        <v>2439.116021870798</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>14003.78216636889</v>
@@ -31252,7 +31252,7 @@
         <v>64372.27159630282</v>
       </c>
       <c r="V68" s="142" t="n">
-        <v>43398.71923906606</v>
+        <v>43398.71923906604</v>
       </c>
       <c r="W68" s="143" t="n">
         <v>6878.522835275839</v>
@@ -31264,7 +31264,7 @@
         <v>15601.11218036403</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>68414.3510911834</v>
+        <v>68414.35109118339</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31782,10 +31782,10 @@
         <v>183.3291939762257</v>
       </c>
       <c r="P76" s="130" t="n">
-        <v>131.7328156641999</v>
+        <v>131.7328156641998</v>
       </c>
       <c r="Q76" s="131" t="n">
-        <v>44.13439203399725</v>
+        <v>44.13439203399726</v>
       </c>
       <c r="R76" s="131" t="n">
         <v>12.44781576517662</v>
@@ -31794,13 +31794,13 @@
         <v>0</v>
       </c>
       <c r="T76" s="132" t="n">
-        <v>188.3150234633738</v>
+        <v>188.3150234633737</v>
       </c>
       <c r="V76" s="130" t="n">
         <v>134.400570669453</v>
       </c>
       <c r="W76" s="131" t="n">
-        <v>45.0557720216745</v>
+        <v>45.05577202167449</v>
       </c>
       <c r="X76" s="131" t="n">
         <v>12.70751077888488</v>
@@ -31846,7 +31846,7 @@
         <v>311.9992424177221</v>
       </c>
       <c r="N77" s="132" t="n">
-        <v>358.769161908742</v>
+        <v>358.7691619087421</v>
       </c>
       <c r="P77" s="130" t="n">
         <v>0</v>
@@ -31968,25 +31968,25 @@
         <v>2439</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>2697.069435486968</v>
+        <v>2697.069435486967</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>111.818241487078</v>
+        <v>111.8182414870779</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>51.21015374407511</v>
+        <v>51.2101537440751</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>10.93331545164582</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>2871.031146169767</v>
+        <v>2871.031146169766</v>
       </c>
       <c r="P79" s="130" t="n">
-        <v>2967.818385277547</v>
+        <v>2967.818385277548</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>141.3309685780186</v>
+        <v>141.3309685780187</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>62.88229397936019</v>
@@ -31995,7 +31995,7 @@
         <v>11.02028858145198</v>
       </c>
       <c r="T79" s="132" t="n">
-        <v>3183.051936416378</v>
+        <v>3183.051936416379</v>
       </c>
       <c r="V79" s="130" t="n">
         <v>3245.047703850661</v>
@@ -32450,7 +32450,7 @@
         <v>57365.21870971905</v>
       </c>
       <c r="M86" s="143" t="n">
-        <v>2922.954135118952</v>
+        <v>2922.954135118953</v>
       </c>
       <c r="N86" s="144" t="n">
         <v>1418321.957026413</v>
@@ -32972,7 +32972,7 @@
         <v>5081</v>
       </c>
       <c r="J94" s="130" t="n">
-        <v>3750.042860748545</v>
+        <v>3750.042860748544</v>
       </c>
       <c r="K94" s="131" t="n">
         <v>1189.94975831014</v>
@@ -32987,13 +32987,13 @@
         <v>5227.306729705846</v>
       </c>
       <c r="P94" s="130" t="n">
-        <v>3803.886503901524</v>
+        <v>3803.886503901523</v>
       </c>
       <c r="Q94" s="131" t="n">
         <v>1222.868012456438</v>
       </c>
       <c r="R94" s="131" t="n">
-        <v>289.1404209483361</v>
+        <v>289.1404209483363</v>
       </c>
       <c r="S94" s="131" t="n">
         <v>0</v>
@@ -33002,13 +33002,13 @@
         <v>5315.894937306298</v>
       </c>
       <c r="V94" s="130" t="n">
-        <v>3862.747772996755</v>
+        <v>3862.747772996754</v>
       </c>
       <c r="W94" s="131" t="n">
         <v>1256.376585107065</v>
       </c>
       <c r="X94" s="131" t="n">
-        <v>290.784476444141</v>
+        <v>290.7844764441409</v>
       </c>
       <c r="Y94" s="131" t="n">
         <v>0</v>
@@ -33060,13 +33060,13 @@
         <v>0</v>
       </c>
       <c r="R95" s="131" t="n">
-        <v>456.6186053665504</v>
+        <v>456.6186053665506</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>4874.628103683081</v>
+        <v>4874.62810368308</v>
       </c>
       <c r="T95" s="132" t="n">
-        <v>5331.246709049631</v>
+        <v>5331.24670904963</v>
       </c>
       <c r="V95" s="130" t="n">
         <v>0</v>
@@ -33176,13 +33176,13 @@
         <v>5407.544268747401</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>821.8541182771899</v>
+        <v>821.8541182771902</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>279.0679125332354</v>
       </c>
       <c r="M97" s="131" t="n">
-        <v>560.645774441062</v>
+        <v>560.6457744410618</v>
       </c>
       <c r="N97" s="132" t="n">
         <v>7069.112073998888</v>
@@ -33191,19 +33191,19 @@
         <v>5816.280603427482</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>901.3963514921277</v>
+        <v>901.396351492128</v>
       </c>
       <c r="R97" s="131" t="n">
-        <v>300.629545753357</v>
+        <v>300.6295457533572</v>
       </c>
       <c r="S97" s="131" t="n">
-        <v>571.6795744008076</v>
+        <v>571.6795744008075</v>
       </c>
       <c r="T97" s="132" t="n">
         <v>7589.986075073774</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>6250.65599672089</v>
+        <v>6250.655996720889</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>987.147598028361</v>
@@ -33212,10 +33212,10 @@
         <v>321.7141332764121</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>593.5213632299141</v>
+        <v>593.5213632299143</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>8153.039091255578</v>
+        <v>8153.039091255577</v>
       </c>
     </row>
     <row r="98">
@@ -33316,10 +33316,10 @@
         <v>140.7306729614211</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>6263.925439571751</v>
+        <v>6263.925439571749</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>9129.730529136657</v>
+        <v>9129.730529136656</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2462.596460303757</v>
@@ -33346,7 +33346,7 @@
         <v>165.5077469208045</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>7864.526914578741</v>
+        <v>7864.526914578742</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>11117.97029900591</v>
@@ -33618,7 +33618,7 @@
         <v>59655.70951589625</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>5336.818379074632</v>
+        <v>5336.818379074633</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1482669.911579746</v>
